--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIII/LTAIPT_A63F13.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIII/LTAIPT_A63F13.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,8 +12,10 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Tabla_435914" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_1_Tabla_435914" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="Hidden_1_Tabla_4359145">Hidden_1_Tabla_435914!$A$1:$A$2</definedName>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$26</definedName>
     <definedName name="Hidden_28">Hidden_2!$A$1:$A$41</definedName>
     <definedName name="Hidden_315">Hidden_3!$A$1:$A$32</definedName>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="219">
   <si>
     <t>48960</t>
   </si>
@@ -242,108 +244,96 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Carretera</t>
+  </si>
+  <si>
+    <t>Miguel N Lira</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>246-46-2-08-12</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>08:30 a 17:30</t>
+  </si>
+  <si>
+    <t>transparencia@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>Se reciben solicitudes de información pública respecto al Colegio de Bachileres del Estado de Tlaxcala, a través del correo electrónico oficial de la Unidad de Transparencia, en el domicilio oficial de ésta, vía telefónica, por correo postal, mensajería, telégrafo, verbalmente ante el personal habilitado que las capturará en el sistema electrónico de solicitudes; o cualquier medio aprobado por el Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>https://www.plataformadetransparencia.org.mx</t>
+  </si>
+  <si>
+    <t>8016474</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>A984CE1C6A57C05A67AB036922DCBFA6</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>8016517</t>
+  </si>
+  <si>
+    <t>12/07/2023</t>
+  </si>
+  <si>
+    <t>Privada</t>
+  </si>
+  <si>
+    <t>Eje vial</t>
+  </si>
+  <si>
+    <t>Circunvalación</t>
+  </si>
+  <si>
+    <t>Brecha</t>
+  </si>
+  <si>
+    <t>Diagonal</t>
   </si>
   <si>
     <t>Calle</t>
   </si>
   <si>
-    <t>Miguel N Lira</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Tlaxcala</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>México</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>transparencia@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>4807308</t>
-  </si>
-  <si>
-    <t>(246)46 6893134</t>
-  </si>
-  <si>
-    <t>08:30 a 14:30 -15:30 a 17:30</t>
-  </si>
-  <si>
-    <t>Se reciben solicitudes de información pública respecto a este sujeto obligado, Colegio de Bachileres del Estado de Tlaxcala, a través del correo electrónico oficial de la Unidad de Transparencia, en el domicilio oficial de ésta, vía telefónica, por correo postal, mensajería, telégrafo, verbalmente ante el personal habilitado que las capturará en el sistema electrónico de solicitudes; o cualquier medio aprobado por el Sistema Nacional de Transaprencia.</t>
-  </si>
-  <si>
-    <t>https://www.plataformadetransparencia.org.mx/</t>
-  </si>
-  <si>
-    <t>4292387</t>
-  </si>
-  <si>
-    <t>1C8F49DBAFFEFAF96B02B378FF4F1995</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>2821907</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
-  </si>
-  <si>
-    <t>Privada</t>
-  </si>
-  <si>
-    <t>2315607</t>
-  </si>
-  <si>
-    <t>Carretera</t>
-  </si>
-  <si>
-    <t>Eje vial</t>
-  </si>
-  <si>
-    <t>Circunvalación</t>
-  </si>
-  <si>
-    <t>Brecha</t>
-  </si>
-  <si>
-    <t>Diagonal</t>
-  </si>
-  <si>
     <t>Corredor</t>
   </si>
   <si>
@@ -611,6 +601,9 @@
     <t>56318</t>
   </si>
   <si>
+    <t>77813</t>
+  </si>
+  <si>
     <t>56319</t>
   </si>
   <si>
@@ -629,361 +622,67 @@
     <t>Segundo apellido</t>
   </si>
   <si>
+    <t>Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Cargo o puesto en el sujeto obligado</t>
   </si>
   <si>
     <t>Cargo o función en la UT</t>
   </si>
   <si>
-    <t>55325B2687A4D1B269CB6D5189D926F5</t>
-  </si>
-  <si>
-    <t>Ma. De los Angeles</t>
-  </si>
-  <si>
-    <t>Acoltzi</t>
-  </si>
-  <si>
-    <t>Parada</t>
+    <t>EF575B64D65263B8C79BD91735AD5241</t>
+  </si>
+  <si>
+    <t>Octavio</t>
+  </si>
+  <si>
+    <t>Carbajal</t>
+  </si>
+  <si>
+    <t>Hernandez</t>
+  </si>
+  <si>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>Secretario de dirección de Plantel</t>
+  </si>
+  <si>
+    <t>Personal habilitado, para dar cumplimiento a las obligaciones de transparencia</t>
+  </si>
+  <si>
+    <t>EF575B64D65263B877D2C04AE1C1836F</t>
+  </si>
+  <si>
+    <t>Martín</t>
+  </si>
+  <si>
+    <t>Gonzalez</t>
+  </si>
+  <si>
+    <t>Técnico especializado B</t>
+  </si>
+  <si>
+    <t>EF575B64D65263B8E10992AF04AF28FE</t>
+  </si>
+  <si>
+    <t>Francisco Rene</t>
+  </si>
+  <si>
+    <t>Zempoalteca</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
   </si>
   <si>
     <t>Capturista</t>
   </si>
   <si>
-    <t>Responsable de cargar la información</t>
-  </si>
-  <si>
-    <t>55325B2687A4D1B25DAEA86C3A419076</t>
-  </si>
-  <si>
-    <t>Maximino</t>
-  </si>
-  <si>
-    <t>Guerra</t>
-  </si>
-  <si>
-    <t>Caporal</t>
-  </si>
-  <si>
-    <t>Tecnico Especializado B</t>
-  </si>
-  <si>
-    <t>55325B2687A4D1B2F4038762030A5229</t>
-  </si>
-  <si>
-    <t>Hugo Jesùs</t>
-  </si>
-  <si>
-    <t>Del Rio</t>
-  </si>
-  <si>
-    <t>Orozco</t>
-  </si>
-  <si>
-    <t>55325B2687A4D1B2787AB3338BAFEABB</t>
-  </si>
-  <si>
-    <t>Francisco Rene</t>
-  </si>
-  <si>
-    <t>Zempoalteca</t>
-  </si>
-  <si>
-    <t>Sánchez</t>
-  </si>
-  <si>
-    <t>55325B2687A4D1B2452980B4C19CBD51</t>
-  </si>
-  <si>
-    <t>Griselda</t>
-  </si>
-  <si>
-    <t>Castro</t>
-  </si>
-  <si>
-    <t>Marquez</t>
-  </si>
-  <si>
-    <t>55325B2687A4D1B2687CED9CD3B37C67</t>
-  </si>
-  <si>
-    <t>Viridiana</t>
-  </si>
-  <si>
-    <t>Meses</t>
-  </si>
-  <si>
-    <t>Aguilar</t>
-  </si>
-  <si>
-    <t>Jefa de Oficina</t>
-  </si>
-  <si>
-    <t>55325B2687A4D1B297BA58507B09ADEF</t>
-  </si>
-  <si>
-    <t>Fernanda</t>
-  </si>
-  <si>
-    <t>Escalante</t>
-  </si>
-  <si>
-    <t>García</t>
-  </si>
-  <si>
-    <t>55325B2687A4D1B20CB0B52E7C402C0F</t>
-  </si>
-  <si>
-    <t>Ma. Guadalupe</t>
-  </si>
-  <si>
-    <t>Muñoz</t>
-  </si>
-  <si>
-    <t>Hernández</t>
-  </si>
-  <si>
-    <t>102BFC03545D4344AB5BBA1118A3602B</t>
-  </si>
-  <si>
-    <t>Luis Alberto</t>
-  </si>
-  <si>
-    <t>Ahuatzi</t>
-  </si>
-  <si>
-    <t>Zecua</t>
-  </si>
-  <si>
-    <t>102BFC03545D43444503DFC9F666543D</t>
-  </si>
-  <si>
-    <t>Mijail</t>
-  </si>
-  <si>
-    <t>Ramirez</t>
-  </si>
-  <si>
-    <t>Amaro</t>
-  </si>
-  <si>
-    <t>Tecnico Espealizado B</t>
-  </si>
-  <si>
-    <t>102BFC03545D4344417E337843D370FB</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>Gomez</t>
-  </si>
-  <si>
-    <t>Matamoros</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento</t>
-  </si>
-  <si>
-    <t>D89662A81A316A0A1ADDA8568664AA1D</t>
-  </si>
-  <si>
-    <t>Técnico Especializado B</t>
-  </si>
-  <si>
-    <t>114A01933870DE9396432D58445A7A92</t>
-  </si>
-  <si>
-    <t>Gómez</t>
-  </si>
-  <si>
-    <t>02CA96C12F48A8C1176F8ED10318EA6C</t>
-  </si>
-  <si>
-    <t>Hugo Jesús</t>
-  </si>
-  <si>
-    <t>84ED330AFA4137CBDF407373AACAFB88</t>
-  </si>
-  <si>
-    <t>Doris</t>
-  </si>
-  <si>
-    <t>Vera</t>
-  </si>
-  <si>
-    <t>Flores</t>
-  </si>
-  <si>
-    <t>F2B46507338D5118E3A754FF06B1CB6E</t>
-  </si>
-  <si>
-    <t>AE3DC546D0F6228D6C7DF92479D5AD1E</t>
-  </si>
-  <si>
-    <t>Ramìrez</t>
-  </si>
-  <si>
-    <t>4B00D9FAF9E5973D32A456219F145983</t>
-  </si>
-  <si>
-    <t>Irving</t>
-  </si>
-  <si>
-    <t>Zaragoza</t>
-  </si>
-  <si>
-    <t>Cruz</t>
-  </si>
-  <si>
-    <t>13B8973A52597D91FF30611C14B55D79</t>
-  </si>
-  <si>
-    <t>ADF7EAFAEC32A1CF71D10E928FB55905</t>
-  </si>
-  <si>
-    <t>César</t>
-  </si>
-  <si>
-    <t>Ortega</t>
-  </si>
-  <si>
-    <t>E124568C0C8ADDEED998578572ECC7C0</t>
-  </si>
-  <si>
-    <t>Eduardo Antonio</t>
-  </si>
-  <si>
-    <t>González</t>
-  </si>
-  <si>
-    <t>Betancour</t>
-  </si>
-  <si>
-    <t>Jefe de Materia</t>
-  </si>
-  <si>
-    <t>Responsable de la Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>D2AFEDE392A79061D817450EDE1EB9A8</t>
-  </si>
-  <si>
-    <t>Sànchez</t>
-  </si>
-  <si>
-    <t>B7AB60C6735EA3B393325012F23268A9</t>
-  </si>
-  <si>
-    <t>5D0A67A2A6C5C5B14F33D312F01BB34C</t>
-  </si>
-  <si>
-    <t>Ma. De los Ángeles</t>
-  </si>
-  <si>
-    <t>1772EE15F5E0ECCAE02705E1A9A26F1B</t>
-  </si>
-  <si>
-    <t>101BFCDA635384FFB81859EFA32C42DD</t>
-  </si>
-  <si>
-    <t>FE83D21BD79C1352972C515021AD309B</t>
-  </si>
-  <si>
-    <t>9A03EA31CA44511FE6747E3CFB0E4FC6</t>
-  </si>
-  <si>
-    <t>169EED90D0B85917782EB206223FA737</t>
-  </si>
-  <si>
-    <t>65480EC8BD297017EFC38E5EB65E2DAA</t>
-  </si>
-  <si>
-    <t>Ivan</t>
-  </si>
-  <si>
-    <t>Romano</t>
-  </si>
-  <si>
-    <t>Morales</t>
-  </si>
-  <si>
-    <t>8C724249234F59CB8C44E18A66F4B82C</t>
-  </si>
-  <si>
-    <t>B25949A1E5AB423EE2630A624A2778EE</t>
-  </si>
-  <si>
-    <t>D1B7C7ADA49191DCBD0355178919FF64</t>
-  </si>
-  <si>
-    <t>0EAD34C4EE5789D6F3B29B0FE8F1218D</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>AE7C8181E930BD26C6C3D46BB59A7BE1</t>
-  </si>
-  <si>
-    <t>1584C1E8E1DC813D93F49331DE1707BD</t>
-  </si>
-  <si>
-    <t>Enrique</t>
-  </si>
-  <si>
-    <t>Cuecuecha</t>
-  </si>
-  <si>
-    <t>Aguila</t>
-  </si>
-  <si>
-    <t>0E275105F494872B5A5EA7906A17BB4D</t>
-  </si>
-  <si>
-    <t>A942DD366ADC51CA0E41DCC4AE332F23</t>
-  </si>
-  <si>
-    <t>E233459CFD3506423EA699EB5D3BEE5E</t>
-  </si>
-  <si>
-    <t>49371C9726C8A746687960CA75E67DD8</t>
-  </si>
-  <si>
-    <t>23232005781B354DBD5BE04DA500A757</t>
-  </si>
-  <si>
-    <t>C86F97F0C1815339127ACA95A17EDEDD</t>
-  </si>
-  <si>
-    <t>Tecnico</t>
-  </si>
-  <si>
-    <t>D35E2C14533893CB999412CAC79163B8</t>
-  </si>
-  <si>
-    <t>6028EC2980262C99A92D4C3A56318981</t>
-  </si>
-  <si>
-    <t>74216F67D8CD243C2A5FE3C83D04C997</t>
-  </si>
-  <si>
-    <t>DC358CCD7C8A47DE9368B44FBE863070</t>
-  </si>
-  <si>
-    <t>Gorge Armando</t>
-  </si>
-  <si>
-    <t>Vivaldo</t>
-  </si>
-  <si>
-    <t>7C1A970118BE07920A6639D11EAEC417</t>
-  </si>
-  <si>
-    <t>Hernàndez</t>
-  </si>
-  <si>
-    <t>04FBDE5CFFE025B8559636E312D8512B</t>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -1382,7 +1081,7 @@
   <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1753,16 +1452,16 @@
     </row>
     <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>73</v>
@@ -1783,61 +1482,61 @@
         <v>78</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>84</v>
       </c>
       <c r="T8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="V8" s="3" t="s">
+      <c r="Y8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y8" s="3" t="s">
+      <c r="Z8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA8" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="AB8" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>76</v>
@@ -1854,13 +1553,13 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E200">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I198">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I200">
       <formula1>Hidden_28</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P8:P198">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P8:P200">
       <formula1>Hidden_315</formula1>
     </dataValidation>
   </dataValidations>
@@ -1875,132 +1574,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2015,22 +1714,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -2040,182 +1739,182 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2230,162 +1929,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2395,19 +2094,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="67" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -2418,1152 +2118,190 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" t="s">
         <v>192</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>193</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="F2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4359145</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>217</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>218</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
